--- a/seguimiento.xlsx
+++ b/seguimiento.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguimiento" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen equipo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por jornada" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]-&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +58,24 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E6B3E"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E4A6B"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B7686"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +90,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAF0F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E6EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -138,6 +175,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2634,4 +2686,254 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Progresión de montos por jornada</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Verde = empató (reinicia $100) · Rojo = no empató (dobla) · Gris = omitido · Azul = próxima</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>J5</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>$1,600</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>$3,200 ✅</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Alavés</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>$400</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>$1,600 ✅</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Rayo</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>⊘</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>$200</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>$400 ✅</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>$200</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>⊘</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>$400</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>R. Sociedad</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>$200</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>$100 ✅*</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>$400</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>* R. Sociedad jugó su empate (vs Celta) adelantado; su progresión no sigue el orden normal de jornadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Al perder, el monto se dobla; al empatar, cobra y reinicia a $100. Actualiza cada jornada.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>